--- a/accountant-skill/data/output/Jul2025/trial_balance_Jul2025.xlsx
+++ b/accountant-skill/data/output/Jul2025/trial_balance_Jul2025.xlsx
@@ -480,7 +480,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dr: 1,097,305,780.77 | Cr: 1,098,519,479.70</t>
+          <t>Dr: 1,570,133,729.29 | Cr: 1,571,347,428.22</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dr: 1,619,886,399.70 | Cr: 1,621,100,098.63</t>
+          <t>Dr: 2,092,190,455.66 | Cr: 2,093,404,154.59</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>308946.6299999999</v>
+        <v>5914123.630000005</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>4790395.09</v>
@@ -658,7 +658,7 @@
         <v>5914124</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>814782.2800000003</v>
+        <v>4790394.720000004</v>
       </c>
     </row>
     <row r="9">
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1317088.449999999</v>
+        <v>9216388.449999999</v>
       </c>
       <c r="D9" s="4" t="n">
         <v>7452014.79</v>
@@ -680,7 +680,7 @@
         <v>9216388</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>447284.7600000016</v>
+        <v>7452015.239999998</v>
       </c>
     </row>
     <row r="10">
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>738174.479999993</v>
+        <v>33723471.52</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>37467131.49</v>
@@ -702,7 +702,7 @@
         <v>33723472</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>3005485.010000005</v>
+        <v>37467131.01000001</v>
       </c>
     </row>
     <row r="11">
@@ -771,12 +771,12 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>210290000</v>
+        <v>429290000</v>
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n">
-        <v>210290000</v>
+        <v>429290000</v>
       </c>
     </row>
     <row r="16">
@@ -788,10 +788,14 @@
           <t>Buildings &amp; Structures</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
+      <c r="C16" s="4" t="n">
+        <v>133000000</v>
+      </c>
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
+      <c r="F16" s="4" t="n">
+        <v>133000000</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -803,14 +807,14 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2770833.68</v>
+        <v>22720833.68000001</v>
       </c>
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n">
         <v>554167</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3325000.68</v>
+        <v>23275000.68000001</v>
       </c>
     </row>
     <row r="18">
@@ -823,14 +827,14 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1520000</v>
+        <v>67920000</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>68000000</v>
       </c>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n">
-        <v>69520000</v>
+        <v>135920000</v>
       </c>
     </row>
     <row r="19">
@@ -843,14 +847,14 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>6003851.33</v>
+        <v>18379151.33</v>
       </c>
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n">
         <v>1651362</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>7655213.33</v>
+        <v>20030513.33</v>
       </c>
     </row>
     <row r="20">
@@ -891,14 +895,14 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>6856000</v>
+        <v>14056000</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>92025000</v>
       </c>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n">
-        <v>98881000</v>
+        <v>106081000</v>
       </c>
     </row>
     <row r="23">
@@ -911,14 +915,14 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1331324.33</v>
+        <v>3041324.33</v>
       </c>
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n">
         <v>367156</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1698480.33</v>
+        <v>3408480.33</v>
       </c>
     </row>
     <row r="24">
@@ -1063,14 +1067,14 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>550000000</v>
+        <v>989530823</v>
       </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n">
         <v>450000000</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1000000000</v>
+        <v>1439530823</v>
       </c>
     </row>
     <row r="34">
@@ -1619,7 +1623,7 @@
       </c>
       <c r="B65" s="6" t="n"/>
       <c r="C65" s="7" t="n">
-        <v>1098519479.7</v>
+        <v>1571347428.22</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>878097330.37</v>
@@ -1628,7 +1632,7 @@
         <v>878097330.37</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>1621100098.63</v>
+        <v>2093404154.59</v>
       </c>
     </row>
   </sheetData>
